--- a/exemplos/misturas_2_7.xlsx
+++ b/exemplos/misturas_2_7.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t>A12:F19: probabilidades antes do limiar, em escala de cores fixa de 0 a 1.</t>
+          <t>Linha 12, lado a lado: matrizes originais, resultado e probabilidades antes do limiar.</t>
         </is>
       </c>
     </row>
@@ -529,174 +529,669 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Original 2 (A)</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Original 7 (B)</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="inlineStr">
         <is>
           <t>Probabilidades</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4">
+      <c r="A12" s="1">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <f>A1</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <f>B1</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <f>C1</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <f>D1</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <f>E1</f>
+        <v>0</v>
+      </c>
+      <c r="T12" s="1">
+        <f>F1</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="4">
         <v>1.2144387449344636e-06</v>
       </c>
-      <c r="B12" s="4">
+      <c r="W12" s="4">
         <v>3.1213680614145264e-06</v>
       </c>
-      <c r="C12" s="4">
+      <c r="X12" s="4">
         <v>3.3721506930515511e-06</v>
       </c>
-      <c r="D12" s="4">
+      <c r="Y12" s="4">
         <v>3.3026361103401666e-06</v>
       </c>
-      <c r="E12" s="4">
+      <c r="Z12" s="4">
         <v>3.0332345719704293e-06</v>
       </c>
-      <c r="F12" s="4">
+      <c r="AA12" s="4">
         <v>1.5743608110939528e-06</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4">
+      <c r="A13" s="1">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <f>A2</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <f>B2</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1">
+        <f>C2</f>
+        <v>1</v>
+      </c>
+      <c r="R13" s="1">
+        <f>D2</f>
+        <v>1</v>
+      </c>
+      <c r="S13" s="1">
+        <f>E2</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="1">
+        <f>F2</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="4">
         <v>1.0372090006495936e-06</v>
       </c>
-      <c r="B13" s="4">
+      <c r="W13" s="4">
         <v>0.00032220721056335259</v>
       </c>
-      <c r="C13" s="4">
+      <c r="X13" s="4">
         <v>0.99997835567074878</v>
       </c>
-      <c r="D13" s="4">
+      <c r="Y13" s="4">
         <v>0.99999958535305067</v>
       </c>
-      <c r="E13" s="4">
+      <c r="Z13" s="4">
         <v>0.00031383900999062465</v>
       </c>
-      <c r="F13" s="4">
+      <c r="AA13" s="4">
         <v>1.2849822519418804e-06</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4">
+      <c r="A14" s="1">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <f>A3</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <f>B3</f>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="1">
+        <f>C3</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <f>D3</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
+        <f>E3</f>
+        <v>1</v>
+      </c>
+      <c r="T14" s="1">
+        <f>F3</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="4">
         <v>1.1296069255834623e-06</v>
       </c>
-      <c r="B14" s="4">
+      <c r="W14" s="4">
         <v>0.99859542797549794</v>
       </c>
-      <c r="C14" s="4">
+      <c r="X14" s="4">
         <v>0.00021433772285512744</v>
       </c>
-      <c r="D14" s="4">
+      <c r="Y14" s="4">
         <v>8.2520984492819499e-07</v>
       </c>
-      <c r="E14" s="4">
+      <c r="Z14" s="4">
         <v>0.99958636387012667</v>
       </c>
-      <c r="F14" s="4">
+      <c r="AA14" s="4">
         <v>8.9659028009384206e-07</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4">
+      <c r="A15" s="1">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <f>A4</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <f>B4</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
+        <f>C4</f>
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <f>D4</f>
+        <v>1</v>
+      </c>
+      <c r="S15" s="1">
+        <f>E4</f>
+        <v>0</v>
+      </c>
+      <c r="T15" s="1">
+        <f>F4</f>
+        <v>0</v>
+      </c>
+      <c r="V15" s="4">
         <v>5.2927038420982011e-07</v>
       </c>
-      <c r="B15" s="4">
+      <c r="W15" s="4">
         <v>0.00061327267260922298</v>
       </c>
-      <c r="C15" s="4">
+      <c r="X15" s="4">
         <v>0.0001611753766393114</v>
       </c>
-      <c r="D15" s="4">
+      <c r="Y15" s="4">
         <v>0.99999977380715055</v>
       </c>
-      <c r="E15" s="4">
+      <c r="Z15" s="4">
         <v>2.6027143254368417e-09</v>
       </c>
-      <c r="F15" s="4">
+      <c r="AA15" s="4">
         <v>1.3172246261496093e-06</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4">
+      <c r="A16" s="1">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <f>A5</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <f>B5</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1">
+        <f>C5</f>
+        <v>1</v>
+      </c>
+      <c r="R16" s="1">
+        <f>D5</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="1">
+        <f>E5</f>
+        <v>0</v>
+      </c>
+      <c r="T16" s="1">
+        <f>F5</f>
+        <v>0</v>
+      </c>
+      <c r="V16" s="4">
         <v>1.4203520334027431e-06</v>
       </c>
-      <c r="B16" s="4">
+      <c r="W16" s="4">
         <v>0.00043281288238118703</v>
       </c>
-      <c r="C16" s="4">
+      <c r="X16" s="4">
         <v>0.99992582029049581</v>
       </c>
-      <c r="D16" s="4">
+      <c r="Y16" s="4">
         <v>1.9827490560297887e-05</v>
       </c>
-      <c r="E16" s="4">
+      <c r="Z16" s="4">
         <v>0.00015390079762084581</v>
       </c>
-      <c r="F16" s="4">
+      <c r="AA16" s="4">
         <v>1.6959651205192253e-06</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4">
+      <c r="A17" s="1">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <f>A6</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <f>B6</f>
+        <v>1</v>
+      </c>
+      <c r="Q17" s="1">
+        <f>C6</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <f>D6</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="1">
+        <f>E6</f>
+        <v>0</v>
+      </c>
+      <c r="T17" s="1">
+        <f>F6</f>
+        <v>0</v>
+      </c>
+      <c r="V17" s="4">
         <v>6.5028735704436984e-07</v>
       </c>
-      <c r="B17" s="4">
+      <c r="W17" s="4">
         <v>0.99999649511222566</v>
       </c>
-      <c r="C17" s="4">
+      <c r="X17" s="4">
         <v>8.5407865433718282e-07</v>
       </c>
-      <c r="D17" s="4">
+      <c r="Y17" s="4">
         <v>0.00020129504459278838</v>
       </c>
-      <c r="E17" s="4">
+      <c r="Z17" s="4">
         <v>0.0001066670019762768</v>
       </c>
-      <c r="F17" s="4">
+      <c r="AA17" s="4">
         <v>4.7062465516213054e-06</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4">
+      <c r="A18" s="1">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <f>A7</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <f>B7</f>
+        <v>1</v>
+      </c>
+      <c r="Q18" s="1">
+        <f>C7</f>
+        <v>1</v>
+      </c>
+      <c r="R18" s="1">
+        <f>D7</f>
+        <v>1</v>
+      </c>
+      <c r="S18" s="1">
+        <f>E7</f>
+        <v>1</v>
+      </c>
+      <c r="T18" s="1">
+        <f>F7</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="4">
         <v>1.1824201606525474e-06</v>
       </c>
-      <c r="B18" s="4">
+      <c r="W18" s="4">
         <v>0.9992528287326693</v>
       </c>
-      <c r="C18" s="4">
+      <c r="X18" s="4">
         <v>0.99895803772612779</v>
       </c>
-      <c r="D18" s="4">
+      <c r="Y18" s="4">
         <v>0.99889324109856714</v>
       </c>
-      <c r="E18" s="4">
+      <c r="Z18" s="4">
         <v>0.99897297314843381</v>
       </c>
-      <c r="F18" s="4">
+      <c r="AA18" s="4">
         <v>8.1723613755583445e-07</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4">
+      <c r="A19" s="1">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <f>A8</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <f>B8</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1">
+        <f>C8</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
+        <f>D8</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="1">
+        <f>E8</f>
+        <v>0</v>
+      </c>
+      <c r="T19" s="1">
+        <f>F8</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="4">
         <v>1.3354785050247709e-06</v>
       </c>
-      <c r="B19" s="4">
+      <c r="W19" s="4">
         <v>1.2306505464918061e-06</v>
       </c>
-      <c r="C19" s="4">
+      <c r="X19" s="4">
         <v>1.3478398930819032e-06</v>
       </c>
-      <c r="D19" s="4">
+      <c r="Y19" s="4">
         <v>8.5236876328100113e-07</v>
       </c>
-      <c r="E19" s="4">
+      <c r="Z19" s="4">
         <v>1.0691094606343498e-06</v>
       </c>
-      <c r="F19" s="4">
+      <c r="AA19" s="4">
         <v>1.0882588414647525e-06</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:F8 H1:BC1">
+  <conditionalFormatting sqref="A1:F8 H1:BC1 A12:F19 H12:M19 O12:T19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0.5</formula>
     </cfRule>
@@ -704,7 +1199,7 @@
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:F19">
+  <conditionalFormatting sqref="V12:AA19">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1086,7 +1581,7 @@
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t>A12:F19: probabilidades antes do limiar, em escala de cores fixa de 0 a 1.</t>
+          <t>Linha 12, lado a lado: matrizes originais, resultado e probabilidades antes do limiar.</t>
         </is>
       </c>
     </row>
@@ -1123,174 +1618,669 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Original 2 (A)</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Original 7 (B)</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="inlineStr">
         <is>
           <t>Probabilidades</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4">
+      <c r="A12" s="1">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <f>A1</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <f>B1</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <f>C1</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <f>D1</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <f>E1</f>
+        <v>0</v>
+      </c>
+      <c r="T12" s="1">
+        <f>F1</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="4">
         <v>1.2670145345655121e-06</v>
       </c>
-      <c r="B12" s="4">
+      <c r="W12" s="4">
         <v>2.994314396654496e-06</v>
       </c>
-      <c r="C12" s="4">
+      <c r="X12" s="4">
         <v>3.2684456190447686e-06</v>
       </c>
-      <c r="D12" s="4">
+      <c r="Y12" s="4">
         <v>3.1587611375913816e-06</v>
       </c>
-      <c r="E12" s="4">
+      <c r="Z12" s="4">
         <v>3.2395932099430836e-06</v>
       </c>
-      <c r="F12" s="4">
+      <c r="AA12" s="4">
         <v>1.5161076130109995e-06</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4">
+      <c r="A13" s="1">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <f>A2</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <f>B2</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1">
+        <f>C2</f>
+        <v>1</v>
+      </c>
+      <c r="R13" s="1">
+        <f>D2</f>
+        <v>1</v>
+      </c>
+      <c r="S13" s="1">
+        <f>E2</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="1">
+        <f>F2</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="4">
         <v>1.0214884252886522e-06</v>
       </c>
-      <c r="B13" s="4">
+      <c r="W13" s="4">
         <v>0.0010651863187854827</v>
       </c>
-      <c r="C13" s="4">
+      <c r="X13" s="4">
         <v>0.99997411601378072</v>
       </c>
-      <c r="D13" s="4">
+      <c r="Y13" s="4">
         <v>0.99999939213966837</v>
       </c>
-      <c r="E13" s="4">
+      <c r="Z13" s="4">
         <v>0.0010499036694876242</v>
       </c>
-      <c r="F13" s="4">
+      <c r="AA13" s="4">
         <v>1.3014075772487376e-06</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4">
+      <c r="A14" s="1">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <f>A3</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <f>B3</f>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="1">
+        <f>C3</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <f>D3</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
+        <f>E3</f>
+        <v>1</v>
+      </c>
+      <c r="T14" s="1">
+        <f>F3</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="4">
         <v>1.1254730649951169e-06</v>
       </c>
-      <c r="B14" s="4">
+      <c r="W14" s="4">
         <v>0.99625719252365941</v>
       </c>
-      <c r="C14" s="4">
+      <c r="X14" s="4">
         <v>0.00015813598634572938</v>
       </c>
-      <c r="D14" s="4">
+      <c r="Y14" s="4">
         <v>1.0470310866069529e-06</v>
       </c>
-      <c r="E14" s="4">
+      <c r="Z14" s="4">
         <v>0.99969313369717128</v>
       </c>
-      <c r="F14" s="4">
+      <c r="AA14" s="4">
         <v>9.0390669437656403e-07</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4">
+      <c r="A15" s="1">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <f>A4</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <f>B4</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
+        <f>C4</f>
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <f>D4</f>
+        <v>1</v>
+      </c>
+      <c r="S15" s="1">
+        <f>E4</f>
+        <v>0</v>
+      </c>
+      <c r="T15" s="1">
+        <f>F4</f>
+        <v>0</v>
+      </c>
+      <c r="V15" s="4">
         <v>5.4976463279445628e-07</v>
       </c>
-      <c r="B15" s="4">
+      <c r="W15" s="4">
         <v>0.00031952949789575927</v>
       </c>
-      <c r="C15" s="4">
+      <c r="X15" s="4">
         <v>0.00014647224067693598</v>
       </c>
-      <c r="D15" s="4">
+      <c r="Y15" s="4">
         <v>0.99999961359242195</v>
       </c>
-      <c r="E15" s="4">
+      <c r="Z15" s="4">
         <v>5.0793779597279013e-09</v>
       </c>
-      <c r="F15" s="4">
+      <c r="AA15" s="4">
         <v>1.3499489999561731e-06</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4">
+      <c r="A16" s="1">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <f>A5</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <f>B5</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1">
+        <f>C5</f>
+        <v>1</v>
+      </c>
+      <c r="R16" s="1">
+        <f>D5</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="1">
+        <f>E5</f>
+        <v>0</v>
+      </c>
+      <c r="T16" s="1">
+        <f>F5</f>
+        <v>0</v>
+      </c>
+      <c r="V16" s="4">
         <v>1.3827187736179128e-06</v>
       </c>
-      <c r="B16" s="4">
+      <c r="W16" s="4">
         <v>0.0004495859102530194</v>
       </c>
-      <c r="C16" s="4">
+      <c r="X16" s="4">
         <v>0.99992137445960982</v>
       </c>
-      <c r="D16" s="4">
+      <c r="Y16" s="4">
         <v>2.4157922406476391e-05</v>
       </c>
-      <c r="E16" s="4">
+      <c r="Z16" s="4">
         <v>0.00013820364410800951</v>
       </c>
-      <c r="F16" s="4">
+      <c r="AA16" s="4">
         <v>1.6922684996768491e-06</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4">
+      <c r="A17" s="1">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <f>A6</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <f>B6</f>
+        <v>1</v>
+      </c>
+      <c r="Q17" s="1">
+        <f>C6</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <f>D6</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="1">
+        <f>E6</f>
+        <v>0</v>
+      </c>
+      <c r="T17" s="1">
+        <f>F6</f>
+        <v>0</v>
+      </c>
+      <c r="V17" s="4">
         <v>6.6120927399795441e-07</v>
       </c>
-      <c r="B17" s="4">
+      <c r="W17" s="4">
         <v>0.99999477567447892</v>
       </c>
-      <c r="C17" s="4">
+      <c r="X17" s="4">
         <v>9.094773423328631e-07</v>
       </c>
-      <c r="D17" s="4">
+      <c r="Y17" s="4">
         <v>0.00014629358252932589</v>
       </c>
-      <c r="E17" s="4">
+      <c r="Z17" s="4">
         <v>0.00011651768948819043</v>
       </c>
-      <c r="F17" s="4">
+      <c r="AA17" s="4">
         <v>4.4606788443612132e-06</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4">
+      <c r="A18" s="1">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <f>A7</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <f>B7</f>
+        <v>1</v>
+      </c>
+      <c r="Q18" s="1">
+        <f>C7</f>
+        <v>1</v>
+      </c>
+      <c r="R18" s="1">
+        <f>D7</f>
+        <v>1</v>
+      </c>
+      <c r="S18" s="1">
+        <f>E7</f>
+        <v>1</v>
+      </c>
+      <c r="T18" s="1">
+        <f>F7</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="4">
         <v>1.168658878330399e-06</v>
       </c>
-      <c r="B18" s="4">
+      <c r="W18" s="4">
         <v>0.99928298774838853</v>
       </c>
-      <c r="C18" s="4">
+      <c r="X18" s="4">
         <v>0.99656174408854925</v>
       </c>
-      <c r="D18" s="4">
+      <c r="Y18" s="4">
         <v>0.99642554021242302</v>
       </c>
-      <c r="E18" s="4">
+      <c r="Z18" s="4">
         <v>0.99727140570892547</v>
       </c>
-      <c r="F18" s="4">
+      <c r="AA18" s="4">
         <v>8.5994361684442255e-07</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4">
+      <c r="A19" s="1">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <f>A8</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <f>B8</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1">
+        <f>C8</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
+        <f>D8</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="1">
+        <f>E8</f>
+        <v>0</v>
+      </c>
+      <c r="T19" s="1">
+        <f>F8</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="4">
         <v>1.3482557484951457e-06</v>
       </c>
-      <c r="B19" s="4">
+      <c r="W19" s="4">
         <v>1.3265459546446295e-06</v>
       </c>
-      <c r="C19" s="4">
+      <c r="X19" s="4">
         <v>1.4485904419621336e-06</v>
       </c>
-      <c r="D19" s="4">
+      <c r="Y19" s="4">
         <v>9.1422960557073027e-07</v>
       </c>
-      <c r="E19" s="4">
+      <c r="Z19" s="4">
         <v>1.1518170094594996e-06</v>
       </c>
-      <c r="F19" s="4">
+      <c r="AA19" s="4">
         <v>1.1610456688134604e-06</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:F8 H1:BC1">
+  <conditionalFormatting sqref="A1:F8 H1:BC1 A12:F19 H12:M19 O12:T19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0.5</formula>
     </cfRule>
@@ -1298,7 +2288,7 @@
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:F19">
+  <conditionalFormatting sqref="V12:AA19">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1680,7 +2670,7 @@
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t>A12:F19: probabilidades antes do limiar, em escala de cores fixa de 0 a 1.</t>
+          <t>Linha 12, lado a lado: matrizes originais, resultado e probabilidades antes do limiar.</t>
         </is>
       </c>
     </row>
@@ -1717,174 +2707,669 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Original 2 (A)</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Original 7 (B)</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="inlineStr">
         <is>
           <t>Probabilidades</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4">
+      <c r="A12" s="1">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <f>A1</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <f>B1</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <f>C1</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <f>D1</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <f>E1</f>
+        <v>0</v>
+      </c>
+      <c r="T12" s="1">
+        <f>F1</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="4">
         <v>3.4301039835048542e-06</v>
       </c>
-      <c r="B12" s="4">
+      <c r="W12" s="4">
         <v>4.7404987357366281e-06</v>
       </c>
-      <c r="C12" s="4">
+      <c r="X12" s="4">
         <v>5.8334345040381772e-06</v>
       </c>
-      <c r="D12" s="4">
+      <c r="Y12" s="4">
         <v>5.0306827724037312e-06</v>
       </c>
-      <c r="E12" s="4">
+      <c r="Z12" s="4">
         <v>8.2159350310586614e-06</v>
       </c>
-      <c r="F12" s="4">
+      <c r="AA12" s="4">
         <v>2.8539156517192818e-06</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4">
+      <c r="A13" s="1">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <f>A2</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <f>B2</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1">
+        <f>C2</f>
+        <v>1</v>
+      </c>
+      <c r="R13" s="1">
+        <f>D2</f>
+        <v>1</v>
+      </c>
+      <c r="S13" s="1">
+        <f>E2</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="1">
+        <f>F2</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="4">
         <v>1.9408793471151601e-06</v>
       </c>
-      <c r="B13" s="4">
+      <c r="W13" s="4">
         <v>0.41626386335612936</v>
       </c>
-      <c r="C13" s="4">
+      <c r="X13" s="4">
         <v>0.99989371066224586</v>
       </c>
-      <c r="D13" s="4">
+      <c r="Y13" s="4">
         <v>0.99999505100122443</v>
       </c>
-      <c r="E13" s="4">
+      <c r="Z13" s="4">
         <v>0.4086296686296601</v>
       </c>
-      <c r="F13" s="4">
+      <c r="AA13" s="4">
         <v>2.7149968165549439e-06</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4">
+      <c r="A14" s="1">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <f>A3</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <f>B3</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
+        <f>C3</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <f>D3</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
+        <f>E3</f>
+        <v>1</v>
+      </c>
+      <c r="T14" s="1">
+        <f>F3</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="4">
         <v>2.394239812916113e-06</v>
       </c>
-      <c r="B14" s="4">
+      <c r="W14" s="4">
         <v>0.30367926121095073</v>
       </c>
-      <c r="C14" s="4">
+      <c r="X14" s="4">
         <v>6.7680333651644347e-05</v>
       </c>
-      <c r="D14" s="4">
+      <c r="Y14" s="4">
         <v>1.7971737687442105e-05</v>
       </c>
-      <c r="E14" s="4">
+      <c r="Z14" s="4">
         <v>0.99985507653758199</v>
       </c>
-      <c r="F14" s="4">
+      <c r="AA14" s="4">
         <v>1.831485091751571e-06</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4">
+      <c r="A15" s="1">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <f>A4</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <f>B4</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
+        <f>C4</f>
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <f>D4</f>
+        <v>1</v>
+      </c>
+      <c r="S15" s="1">
+        <f>E4</f>
+        <v>0</v>
+      </c>
+      <c r="T15" s="1">
+        <f>F4</f>
+        <v>0</v>
+      </c>
+      <c r="V15" s="4">
         <v>1.3224722964857992e-06</v>
       </c>
-      <c r="B15" s="4">
+      <c r="W15" s="4">
         <v>6.2247589907053665e-06</v>
       </c>
-      <c r="C15" s="4">
+      <c r="X15" s="4">
         <v>7.899858804456876e-05</v>
       </c>
-      <c r="D15" s="4">
+      <c r="Y15" s="4">
         <v>0.99999012717164726</v>
       </c>
-      <c r="E15" s="4">
+      <c r="Z15" s="4">
         <v>6.4741904421862729e-08</v>
       </c>
-      <c r="F15" s="4">
+      <c r="AA15" s="4">
         <v>2.9047979430773891e-06</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4">
+      <c r="A16" s="1">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <f>A5</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <f>B5</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1">
+        <f>C5</f>
+        <v>1</v>
+      </c>
+      <c r="R16" s="1">
+        <f>D5</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="1">
+        <f>E5</f>
+        <v>0</v>
+      </c>
+      <c r="T16" s="1">
+        <f>F5</f>
+        <v>0</v>
+      </c>
+      <c r="V16" s="4">
         <v>2.5174738780962665e-06</v>
       </c>
-      <c r="B16" s="4">
+      <c r="W16" s="4">
         <v>0.0003358835014817965</v>
       </c>
-      <c r="C16" s="4">
+      <c r="X16" s="4">
         <v>0.99990948794563461</v>
       </c>
-      <c r="D16" s="4">
+      <c r="Y16" s="4">
         <v>0.00021042380938649197</v>
       </c>
-      <c r="E16" s="4">
+      <c r="Z16" s="4">
         <v>2.5746255517457121e-05</v>
       </c>
-      <c r="F16" s="4">
+      <c r="AA16" s="4">
         <v>3.2344184570066994e-06</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4">
+      <c r="A17" s="1">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <f>A6</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <f>B6</f>
+        <v>1</v>
+      </c>
+      <c r="Q17" s="1">
+        <f>C6</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <f>D6</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="1">
+        <f>E6</f>
+        <v>0</v>
+      </c>
+      <c r="T17" s="1">
+        <f>F6</f>
+        <v>0</v>
+      </c>
+      <c r="V17" s="4">
         <v>1.5736473688621569e-06</v>
       </c>
-      <c r="B17" s="4">
+      <c r="W17" s="4">
         <v>0.99996018732138636</v>
       </c>
-      <c r="C17" s="4">
+      <c r="X17" s="4">
         <v>2.6052334512851163e-06</v>
       </c>
-      <c r="D17" s="4">
+      <c r="Y17" s="4">
         <v>6.2629900258191453e-05</v>
       </c>
-      <c r="E17" s="4">
+      <c r="Z17" s="4">
         <v>7.9450619012007214e-05</v>
       </c>
-      <c r="F17" s="4">
+      <c r="AA17" s="4">
         <v>6.5163520273200469e-06</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4">
+      <c r="A18" s="1">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <f>A7</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <f>B7</f>
+        <v>1</v>
+      </c>
+      <c r="Q18" s="1">
+        <f>C7</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <f>D7</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="1">
+        <f>E7</f>
+        <v>1</v>
+      </c>
+      <c r="T18" s="1">
+        <f>F7</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="4">
         <v>2.2090615183269997e-06</v>
       </c>
-      <c r="B18" s="4">
+      <c r="W18" s="4">
         <v>0.99962793251732041</v>
       </c>
-      <c r="C18" s="4">
+      <c r="X18" s="4">
         <v>0.34820544030211659</v>
       </c>
-      <c r="D18" s="4">
+      <c r="Y18" s="4">
         <v>0.34308276736118737</v>
       </c>
-      <c r="E18" s="4">
+      <c r="Z18" s="4">
         <v>0.60202121062300518</v>
       </c>
-      <c r="F18" s="4">
+      <c r="AA18" s="4">
         <v>2.1261912043890959e-06</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4">
+      <c r="A19" s="1">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <f>A8</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <f>B8</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1">
+        <f>C8</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
+        <f>D8</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="1">
+        <f>E8</f>
+        <v>0</v>
+      </c>
+      <c r="T19" s="1">
+        <f>F8</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="4">
         <v>3.0317922389856613e-06</v>
       </c>
-      <c r="B19" s="4">
+      <c r="W19" s="4">
         <v>3.4606774330591237e-06</v>
       </c>
-      <c r="C19" s="4">
+      <c r="X19" s="4">
         <v>4.3759770446617515e-06</v>
       </c>
-      <c r="D19" s="4">
+      <c r="Y19" s="4">
         <v>2.6333408383508855e-06</v>
       </c>
-      <c r="E19" s="4">
+      <c r="Z19" s="4">
         <v>3.3428809427112916e-06</v>
       </c>
-      <c r="F19" s="4">
+      <c r="AA19" s="4">
         <v>3.063457747071862e-06</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:F8 H1:BC1">
+  <conditionalFormatting sqref="A1:F8 H1:BC1 A12:F19 H12:M19 O12:T19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0.5</formula>
     </cfRule>
@@ -1892,7 +3377,7 @@
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:F19">
+  <conditionalFormatting sqref="V12:AA19">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2274,7 +3759,7 @@
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t>A12:F19: probabilidades antes do limiar, em escala de cores fixa de 0 a 1.</t>
+          <t>Linha 12, lado a lado: matrizes originais, resultado e probabilidades antes do limiar.</t>
         </is>
       </c>
     </row>
@@ -2311,174 +3796,669 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Original 2 (A)</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Original 7 (B)</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="inlineStr">
         <is>
           <t>Probabilidades</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4">
+      <c r="A12" s="1">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <f>A1</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <f>B1</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <f>C1</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <f>D1</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <f>E1</f>
+        <v>0</v>
+      </c>
+      <c r="T12" s="1">
+        <f>F1</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="4">
         <v>2.4435032699594072e-05</v>
       </c>
-      <c r="B12" s="4">
+      <c r="W12" s="4">
         <v>1.7147837613567224e-05</v>
       </c>
-      <c r="C12" s="4">
+      <c r="X12" s="4">
         <v>2.4934601687428504e-05</v>
       </c>
-      <c r="D12" s="4">
+      <c r="Y12" s="4">
         <v>2.0209431126130444e-05</v>
       </c>
-      <c r="E12" s="4">
+      <c r="Z12" s="4">
         <v>4.5860657886355227e-05</v>
       </c>
-      <c r="F12" s="4">
+      <c r="AA12" s="4">
         <v>1.5603630391796763e-05</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4">
+      <c r="A13" s="1">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <f>A2</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <f>B2</f>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="1">
+        <f>C2</f>
+        <v>1</v>
+      </c>
+      <c r="R13" s="1">
+        <f>D2</f>
+        <v>1</v>
+      </c>
+      <c r="S13" s="1">
+        <f>E2</f>
+        <v>1</v>
+      </c>
+      <c r="T13" s="1">
+        <f>F2</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="4">
         <v>1.1117840712115268e-05</v>
       </c>
-      <c r="B13" s="4">
+      <c r="W13" s="4">
         <v>0.99900528870645988</v>
       </c>
-      <c r="C13" s="4">
+      <c r="X13" s="4">
         <v>0.99982679605340785</v>
       </c>
-      <c r="D13" s="4">
+      <c r="Y13" s="4">
         <v>0.99996105255989687</v>
       </c>
-      <c r="E13" s="4">
+      <c r="Z13" s="4">
         <v>0.99911773696178774</v>
       </c>
-      <c r="F13" s="4">
+      <c r="AA13" s="4">
         <v>1.593684585191867e-05</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4">
+      <c r="A14" s="1">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <f>A3</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <f>B3</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
+        <f>C3</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <f>D3</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
+        <f>E3</f>
+        <v>1</v>
+      </c>
+      <c r="T14" s="1">
+        <f>F3</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="4">
         <v>1.5536287873995971e-05</v>
       </c>
-      <c r="B14" s="4">
+      <c r="W14" s="4">
         <v>0.00063140772692185166</v>
       </c>
-      <c r="C14" s="4">
+      <c r="X14" s="4">
         <v>1.1888905773449289e-05</v>
       </c>
-      <c r="D14" s="4">
+      <c r="Y14" s="4">
         <v>0.00015171082966289207</v>
       </c>
-      <c r="E14" s="4">
+      <c r="Z14" s="4">
         <v>0.9999256209663272</v>
       </c>
-      <c r="F14" s="4">
+      <c r="AA14" s="4">
         <v>1.1139992606130001e-05</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4">
+      <c r="A15" s="1">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <f>A4</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <f>B4</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
+        <f>C4</f>
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <f>D4</f>
+        <v>1</v>
+      </c>
+      <c r="S15" s="1">
+        <f>E4</f>
+        <v>0</v>
+      </c>
+      <c r="T15" s="1">
+        <f>F4</f>
+        <v>0</v>
+      </c>
+      <c r="V15" s="4">
         <v>9.8487657011592647e-06</v>
       </c>
-      <c r="B15" s="4">
+      <c r="W15" s="4">
         <v>2.7232374372140935e-07</v>
       </c>
-      <c r="C15" s="4">
+      <c r="X15" s="4">
         <v>0.00014850781658353409</v>
       </c>
-      <c r="D15" s="4">
+      <c r="Y15" s="4">
         <v>0.99981458130816048</v>
       </c>
-      <c r="E15" s="4">
+      <c r="Z15" s="4">
         <v>8.9324424372421726e-07</v>
       </c>
-      <c r="F15" s="4">
+      <c r="AA15" s="4">
         <v>1.5006952011748865e-05</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4">
+      <c r="A16" s="1">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <f>A5</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <f>B5</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1">
+        <f>C5</f>
+        <v>1</v>
+      </c>
+      <c r="R16" s="1">
+        <f>D5</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="1">
+        <f>E5</f>
+        <v>0</v>
+      </c>
+      <c r="T16" s="1">
+        <f>F5</f>
+        <v>0</v>
+      </c>
+      <c r="V16" s="4">
         <v>1.5651905800608859e-05</v>
       </c>
-      <c r="B16" s="4">
+      <c r="W16" s="4">
         <v>0.00026546355163604117</v>
       </c>
-      <c r="C16" s="4">
+      <c r="X16" s="4">
         <v>0.99992073227486511</v>
       </c>
-      <c r="D16" s="4">
+      <c r="Y16" s="4">
         <v>0.00037349816130269304</v>
       </c>
-      <c r="E16" s="4">
+      <c r="Z16" s="4">
         <v>1.3390588954410889e-05</v>
       </c>
-      <c r="F16" s="4">
+      <c r="AA16" s="4">
         <v>1.7950676284824625e-05</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4">
+      <c r="A17" s="1">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <f>A6</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <f>B6</f>
+        <v>1</v>
+      </c>
+      <c r="Q17" s="1">
+        <f>C6</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <f>D6</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="1">
+        <f>E6</f>
+        <v>0</v>
+      </c>
+      <c r="T17" s="1">
+        <f>F6</f>
+        <v>0</v>
+      </c>
+      <c r="V17" s="4">
         <v>1.0743395533670377e-05</v>
       </c>
-      <c r="B17" s="4">
+      <c r="W17" s="4">
         <v>0.9998983957611447</v>
       </c>
-      <c r="C17" s="4">
+      <c r="X17" s="4">
         <v>1.7528050919194136e-05</v>
       </c>
-      <c r="D17" s="4">
+      <c r="Y17" s="4">
         <v>1.0231844424593181e-05</v>
       </c>
-      <c r="E17" s="4">
+      <c r="Z17" s="4">
         <v>5.4837878387943027e-05</v>
       </c>
-      <c r="F17" s="4">
+      <c r="AA17" s="4">
         <v>2.4004128907193096e-05</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4">
+      <c r="A18" s="1">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <f>A7</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <f>B7</f>
+        <v>1</v>
+      </c>
+      <c r="Q18" s="1">
+        <f>C7</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <f>D7</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="1">
+        <f>E7</f>
+        <v>0</v>
+      </c>
+      <c r="T18" s="1">
+        <f>F7</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="4">
         <v>1.3131677245881475e-05</v>
       </c>
-      <c r="B18" s="4">
+      <c r="W18" s="4">
         <v>0.99996236991217602</v>
       </c>
-      <c r="C18" s="4">
+      <c r="X18" s="4">
         <v>0.00082536432456412404</v>
       </c>
-      <c r="D18" s="4">
+      <c r="Y18" s="4">
         <v>0.0007964027152508969</v>
       </c>
-      <c r="E18" s="4">
+      <c r="Z18" s="4">
         <v>0.0038002372615423591</v>
       </c>
-      <c r="F18" s="4">
+      <c r="AA18" s="4">
         <v>1.669915695431457e-05</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4">
+      <c r="A19" s="1">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <f>A8</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <f>B8</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1">
+        <f>C8</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
+        <f>D8</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="1">
+        <f>E8</f>
+        <v>0</v>
+      </c>
+      <c r="T19" s="1">
+        <f>F8</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="4">
         <v>1.8098061394784322e-05</v>
       </c>
-      <c r="B19" s="4">
+      <c r="W19" s="4">
         <v>2.4099510610389841e-05</v>
       </c>
-      <c r="C19" s="4">
+      <c r="X19" s="4">
         <v>2.740927936615247e-05</v>
       </c>
-      <c r="D19" s="4">
+      <c r="Y19" s="4">
         <v>1.9672601002128978e-05</v>
       </c>
-      <c r="E19" s="4">
+      <c r="Z19" s="4">
         <v>2.5675170421588104e-05</v>
       </c>
-      <c r="F19" s="4">
+      <c r="AA19" s="4">
         <v>1.9002033541657955e-05</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:F8 H1:BC1">
+  <conditionalFormatting sqref="A1:F8 H1:BC1 A12:F19 H12:M19 O12:T19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0.5</formula>
     </cfRule>
@@ -2486,7 +4466,7 @@
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:F19">
+  <conditionalFormatting sqref="V12:AA19">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2868,7 +4848,7 @@
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t>A12:F19: probabilidades antes do limiar, em escala de cores fixa de 0 a 1.</t>
+          <t>Linha 12, lado a lado: matrizes originais, resultado e probabilidades antes do limiar.</t>
         </is>
       </c>
     </row>
@@ -2905,174 +4885,669 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Original 2 (A)</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Original 7 (B)</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="inlineStr">
         <is>
           <t>Probabilidades</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4">
+      <c r="A12" s="1">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <f>A1</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <f>B1</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <f>C1</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <f>D1</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <f>E1</f>
+        <v>0</v>
+      </c>
+      <c r="T12" s="1">
+        <f>F1</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="4">
         <v>3.9487070318816474e-05</v>
       </c>
-      <c r="B12" s="4">
+      <c r="W12" s="4">
         <v>2.3671413762187114e-05</v>
       </c>
-      <c r="C12" s="4">
+      <c r="X12" s="4">
         <v>3.5268917665106903e-05</v>
       </c>
-      <c r="D12" s="4">
+      <c r="Y12" s="4">
         <v>2.8370838338223173e-05</v>
       </c>
-      <c r="E12" s="4">
+      <c r="Z12" s="4">
         <v>6.9218391329236336e-05</v>
       </c>
-      <c r="F12" s="4">
+      <c r="AA12" s="4">
         <v>2.3639460564054734e-05</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4">
+      <c r="A13" s="1">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <f>A2</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <f>B2</f>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="1">
+        <f>C2</f>
+        <v>1</v>
+      </c>
+      <c r="R13" s="1">
+        <f>D2</f>
+        <v>1</v>
+      </c>
+      <c r="S13" s="1">
+        <f>E2</f>
+        <v>1</v>
+      </c>
+      <c r="T13" s="1">
+        <f>F2</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="4">
         <v>1.7476823277432704e-05</v>
       </c>
-      <c r="B13" s="4">
+      <c r="W13" s="4">
         <v>0.99982033965451544</v>
       </c>
-      <c r="C13" s="4">
+      <c r="X13" s="4">
         <v>0.9998033604493648</v>
       </c>
-      <c r="D13" s="4">
+      <c r="Y13" s="4">
         <v>0.99993163050571077</v>
       </c>
-      <c r="E13" s="4">
+      <c r="Z13" s="4">
         <v>0.99985358107197719</v>
       </c>
-      <c r="F13" s="4">
+      <c r="AA13" s="4">
         <v>2.5143999246642752e-05</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4">
+      <c r="A14" s="1">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <f>A3</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <f>B3</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
+        <f>C3</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <f>D3</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
+        <f>E3</f>
+        <v>1</v>
+      </c>
+      <c r="T14" s="1">
+        <f>F3</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="4">
         <v>2.4746962960588723e-05</v>
       </c>
-      <c r="B14" s="4">
+      <c r="W14" s="4">
         <v>0.00016952006250331808</v>
       </c>
-      <c r="C14" s="4">
+      <c r="X14" s="4">
         <v>7.0053957003325349e-06</v>
       </c>
-      <c r="D14" s="4">
+      <c r="Y14" s="4">
         <v>0.00017655358184736478</v>
       </c>
-      <c r="E14" s="4">
+      <c r="Z14" s="4">
         <v>0.99994121490402033</v>
       </c>
-      <c r="F14" s="4">
+      <c r="AA14" s="4">
         <v>1.8070995865646554e-05</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4">
+      <c r="A15" s="1">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <f>A4</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <f>B4</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
+        <f>C4</f>
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <f>D4</f>
+        <v>1</v>
+      </c>
+      <c r="S15" s="1">
+        <f>E4</f>
+        <v>0</v>
+      </c>
+      <c r="T15" s="1">
+        <f>F4</f>
+        <v>0</v>
+      </c>
+      <c r="V15" s="4">
         <v>1.6323354574200282e-05</v>
       </c>
-      <c r="B15" s="4">
+      <c r="W15" s="4">
         <v>1.8309945682814586e-07</v>
       </c>
-      <c r="C15" s="4">
+      <c r="X15" s="4">
         <v>0.00019907674054971515</v>
       </c>
-      <c r="D15" s="4">
+      <c r="Y15" s="4">
         <v>0.9996796858320548</v>
       </c>
-      <c r="E15" s="4">
+      <c r="Z15" s="4">
         <v>1.9849281092032011e-06</v>
       </c>
-      <c r="F15" s="4">
+      <c r="AA15" s="4">
         <v>2.2314684715072042e-05</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4">
+      <c r="A16" s="1">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <f>A5</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <f>B5</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1">
+        <f>C5</f>
+        <v>1</v>
+      </c>
+      <c r="R16" s="1">
+        <f>D5</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="1">
+        <f>E5</f>
+        <v>0</v>
+      </c>
+      <c r="T16" s="1">
+        <f>F5</f>
+        <v>0</v>
+      </c>
+      <c r="V16" s="4">
         <v>2.4887135646910483e-05</v>
       </c>
-      <c r="B16" s="4">
+      <c r="W16" s="4">
         <v>0.00029580608216265859</v>
       </c>
-      <c r="C16" s="4">
+      <c r="X16" s="4">
         <v>0.99992518392294349</v>
       </c>
-      <c r="D16" s="4">
+      <c r="Y16" s="4">
         <v>0.00030838535086419967</v>
       </c>
-      <c r="E16" s="4">
+      <c r="Z16" s="4">
         <v>1.7824170895731076e-05</v>
       </c>
-      <c r="F16" s="4">
+      <c r="AA16" s="4">
         <v>2.7349389606433658e-05</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4">
+      <c r="A17" s="1">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <f>A6</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <f>B6</f>
+        <v>1</v>
+      </c>
+      <c r="Q17" s="1">
+        <f>C6</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <f>D6</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="1">
+        <f>E6</f>
+        <v>0</v>
+      </c>
+      <c r="T17" s="1">
+        <f>F6</f>
+        <v>0</v>
+      </c>
+      <c r="V17" s="4">
         <v>1.6814798398730858e-05</v>
       </c>
-      <c r="B17" s="4">
+      <c r="W17" s="4">
         <v>0.99987366014766876</v>
       </c>
-      <c r="C17" s="4">
+      <c r="X17" s="4">
         <v>2.723202860624439e-05</v>
       </c>
-      <c r="D17" s="4">
+      <c r="Y17" s="4">
         <v>5.8276438833346635e-06</v>
       </c>
-      <c r="E17" s="4">
+      <c r="Z17" s="4">
         <v>5.698122487070506e-05</v>
       </c>
-      <c r="F17" s="4">
+      <c r="AA17" s="4">
         <v>3.3443930054403363e-05</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4">
+      <c r="A18" s="1">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <f>A7</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <f>B7</f>
+        <v>1</v>
+      </c>
+      <c r="Q18" s="1">
+        <f>C7</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <f>D7</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="1">
+        <f>E7</f>
+        <v>0</v>
+      </c>
+      <c r="T18" s="1">
+        <f>F7</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="4">
         <v>2.1251392332544335e-05</v>
       </c>
-      <c r="B18" s="4">
+      <c r="W18" s="4">
         <v>0.99997851891398126</v>
       </c>
-      <c r="C18" s="4">
+      <c r="X18" s="4">
         <v>0.00018530538495452003</v>
       </c>
-      <c r="D18" s="4">
+      <c r="Y18" s="4">
         <v>0.00018140079910218443</v>
       </c>
-      <c r="E18" s="4">
+      <c r="Z18" s="4">
         <v>0.0011887816469097236</v>
       </c>
-      <c r="F18" s="4">
+      <c r="AA18" s="4">
         <v>2.8780645600378627e-05</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4">
+      <c r="A19" s="1">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <f>A8</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <f>B8</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1">
+        <f>C8</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
+        <f>D8</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="1">
+        <f>E8</f>
+        <v>0</v>
+      </c>
+      <c r="T19" s="1">
+        <f>F8</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="4">
         <v>2.7716311291244694e-05</v>
       </c>
-      <c r="B19" s="4">
+      <c r="W19" s="4">
         <v>3.9950476624472849e-05</v>
       </c>
-      <c r="C19" s="4">
+      <c r="X19" s="4">
         <v>4.1206377117954084e-05</v>
       </c>
-      <c r="D19" s="4">
+      <c r="Y19" s="4">
         <v>3.2802317171637209e-05</v>
       </c>
-      <c r="E19" s="4">
+      <c r="Z19" s="4">
         <v>4.28908453566264e-05</v>
       </c>
-      <c r="F19" s="4">
+      <c r="AA19" s="4">
         <v>2.9373736164241245e-05</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:F8 H1:BC1">
+  <conditionalFormatting sqref="A1:F8 H1:BC1 A12:F19 H12:M19 O12:T19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0.5</formula>
     </cfRule>
@@ -3080,7 +5555,7 @@
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:F19">
+  <conditionalFormatting sqref="V12:AA19">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
